--- a/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
+++ b/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan\Documents\state-eps-data-repository\LA\trans\AVLo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\AVLo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B90D9E6-2397-4F64-9B11-9A12778FCFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AC2DF5-4868-4C3C-8298-C8F8D01CCD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="502">
   <si>
     <t>AVLo Average Vehicle Loading</t>
   </si>
@@ -2538,7 +2538,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2684,7 +2684,6 @@
     <xf numFmtId="11" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="157">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3177,25 +3176,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="85.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C1" s="81">
-        <v>45313</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3203,57 +3196,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:2">
       <c r="B5" s="2">
         <v>2009</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:2">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:2">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:2">
       <c r="B12" s="2">
         <v>2008</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:2">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>11</v>
       </c>
